--- a/fifa_2026_sticker_trade.xlsx
+++ b/fifa_2026_sticker_trade.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="248">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -111,9 +111,6 @@
     <t xml:space="preserve">MEX_8</t>
   </si>
   <si>
-    <t xml:space="preserve">MEX_10</t>
-  </si>
-  <si>
     <t xml:space="preserve">South Africa</t>
   </si>
   <si>
@@ -135,658 +132,631 @@
     <t xml:space="preserve">KOR_10</t>
   </si>
   <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAN_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAN_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bosnia-Herzegovina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIH_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIH_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qatar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QAT_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QAT_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switzerland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUI_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRA_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRA_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRA_18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morocco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAR_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAI_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAI_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scotland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCO_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCO_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paraguay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAR_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAR_20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUS_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUS_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUS_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUS_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Türkiye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUR_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUR_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUR_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GER_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curaçao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUW_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUW_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUW_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Côte d'Ivoire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIV_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIV_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIV_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecuador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECU_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECU_18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netherlands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NED_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPN_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPN_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPN_18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWE_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tunisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUN_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUN_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUN_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUN_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belgium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEL_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEL_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egypt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGY_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGY_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGY_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGY_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IR Iran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRN_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRN_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRN_20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Zealand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NZL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NZL_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NZL_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESP_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabo Verde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPV_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saudi Arabia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KSA_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KSA_20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uruguay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URU_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URU_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRA_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRA_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRA_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRA_20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senegal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEN_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iraq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRQ_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRQ_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOR_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOR_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOR_18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argentina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARG_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARG_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARG_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARG_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algeria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALG_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALG_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALG_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALG_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALG_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUT_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUT_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUT_18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUT_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOR_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portugal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POR_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POR_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POR_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POR_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Congo DR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COD_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COD_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uzbekistan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UZB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UZB_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UZB_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">England</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croatia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRO_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GHA_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GHA_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN_16</t>
+  </si>
+  <si>
     <t xml:space="preserve">Czechia</t>
   </si>
   <si>
     <t xml:space="preserve">CZE</t>
   </si>
   <si>
-    <t xml:space="preserve">CZE_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAN_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAN_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bosnia-Herzegovina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIH_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIH_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qatar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QAT_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QAT_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switzerland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUI_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRA_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRA_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRA_18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morocco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAR_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haiti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAI_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAI_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scotland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCO_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCO_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USA_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paraguay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAR_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAR_20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Australia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUS_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUS_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUS_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUS_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Türkiye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUR_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUR_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUR_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GER_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curaçao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUW_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUW_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUW_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Côte d'Ivoire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIV_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIV_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIV_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecuador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECU_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECU_18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netherlands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NED_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Japan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JPN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JPN_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JPN_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JPN_18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SWE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SWE_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tunisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUN_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUN_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUN_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUN_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belgium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEL_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEL_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egypt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EGY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EGY_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EGY_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EGY_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EGY_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IR Iran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRN_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRN_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRN_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRN_20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Zealand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NZL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NZL_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NZL_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESP_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabo Verde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPV_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saudi Arabia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KSA_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KSA_20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uruguay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URU_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URU_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRA_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRA_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRA_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRA_20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senegal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEN_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEN_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iraq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRQ_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRQ_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Norway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOR_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOR_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOR_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOR_18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argentina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARG_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARG_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARG_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARG_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algeria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALG_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALG_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALG_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALG_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALG_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALG_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUT_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUT_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUT_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUT_18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUT_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOR_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portugal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POR_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POR_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POR_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POR_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POR_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Congo DR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COD_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COD_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COD_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uzbekistan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UZB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UZB_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UZB_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colombia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">England</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Croatia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRO_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GHA_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GHA_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN_16</t>
-  </si>
-  <si>
     <t xml:space="preserve">World Cup Champions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FWC_14</t>
   </si>
 </sst>
 </file>
@@ -794,7 +764,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -802,13 +772,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -823,8 +804,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1116,73 +1098,73 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1244,9 +1226,7 @@
         <v>31</v>
       </c>
       <c r="L3"/>
-      <c r="M3" t="s">
-        <v>32</v>
-      </c>
+      <c r="M3"/>
       <c r="N3"/>
       <c r="O3"/>
       <c r="P3"/>
@@ -1263,21 +1243,21 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
       <c r="F4"/>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K4"/>
       <c r="L4"/>
@@ -1298,10 +1278,10 @@
         <v>26</v>
       </c>
       <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
         <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>38</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -1313,7 +1293,7 @@
       <c r="K5"/>
       <c r="L5"/>
       <c r="M5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N5"/>
       <c r="O5"/>
@@ -1328,7 +1308,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
         <v>40</v>
@@ -1339,18 +1319,20 @@
       <c r="D6"/>
       <c r="E6"/>
       <c r="F6"/>
-      <c r="G6" t="s">
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6" t="s">
         <v>42</v>
       </c>
-      <c r="H6"/>
-      <c r="I6"/>
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6"/>
       <c r="M6"/>
       <c r="N6"/>
       <c r="O6"/>
-      <c r="P6"/>
+      <c r="P6" t="s">
+        <v>43</v>
+      </c>
       <c r="Q6"/>
       <c r="R6"/>
       <c r="S6"/>
@@ -1361,7 +1343,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
         <v>44</v>
@@ -1370,22 +1352,22 @@
         <v>45</v>
       </c>
       <c r="D7"/>
-      <c r="E7"/>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
       <c r="F7"/>
       <c r="G7"/>
       <c r="H7"/>
-      <c r="I7" t="s">
-        <v>46</v>
-      </c>
+      <c r="I7"/>
       <c r="J7"/>
       <c r="K7"/>
       <c r="L7"/>
       <c r="M7"/>
-      <c r="N7"/>
+      <c r="N7" t="s">
+        <v>47</v>
+      </c>
       <c r="O7"/>
-      <c r="P7" t="s">
-        <v>47</v>
-      </c>
+      <c r="P7"/>
       <c r="Q7"/>
       <c r="R7"/>
       <c r="S7"/>
@@ -1396,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
         <v>48</v>
@@ -1405,9 +1387,7 @@
         <v>49</v>
       </c>
       <c r="D8"/>
-      <c r="E8" t="s">
-        <v>50</v>
-      </c>
+      <c r="E8"/>
       <c r="F8"/>
       <c r="G8"/>
       <c r="H8"/>
@@ -1416,14 +1396,16 @@
       <c r="K8"/>
       <c r="L8"/>
       <c r="M8"/>
-      <c r="N8" t="s">
-        <v>51</v>
-      </c>
+      <c r="N8"/>
       <c r="O8"/>
       <c r="P8"/>
-      <c r="Q8"/>
+      <c r="Q8" t="s">
+        <v>50</v>
+      </c>
       <c r="R8"/>
-      <c r="S8"/>
+      <c r="S8" t="s">
+        <v>51</v>
+      </c>
       <c r="T8"/>
       <c r="U8"/>
       <c r="V8"/>
@@ -1431,7 +1413,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
         <v>52</v>
@@ -1449,16 +1431,14 @@
       <c r="K9"/>
       <c r="L9"/>
       <c r="M9"/>
-      <c r="N9"/>
+      <c r="N9" t="s">
+        <v>54</v>
+      </c>
       <c r="O9"/>
       <c r="P9"/>
-      <c r="Q9" t="s">
-        <v>54</v>
-      </c>
+      <c r="Q9"/>
       <c r="R9"/>
-      <c r="S9" t="s">
-        <v>55</v>
-      </c>
+      <c r="S9"/>
       <c r="T9"/>
       <c r="U9"/>
       <c r="V9"/>
@@ -1466,7 +1446,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
         <v>56</v>
@@ -1476,7 +1456,9 @@
       </c>
       <c r="D10"/>
       <c r="E10"/>
-      <c r="F10"/>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
       <c r="G10"/>
       <c r="H10"/>
       <c r="I10"/>
@@ -1484,34 +1466,36 @@
       <c r="K10"/>
       <c r="L10"/>
       <c r="M10"/>
-      <c r="N10" t="s">
-        <v>58</v>
-      </c>
+      <c r="N10"/>
       <c r="O10"/>
-      <c r="P10"/>
+      <c r="P10" t="s">
+        <v>59</v>
+      </c>
       <c r="Q10"/>
       <c r="R10"/>
       <c r="S10"/>
       <c r="T10"/>
-      <c r="U10"/>
+      <c r="U10" t="s">
+        <v>60</v>
+      </c>
       <c r="V10"/>
       <c r="W10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11"/>
       <c r="G11"/>
       <c r="H11"/>
       <c r="I11"/>
@@ -1521,34 +1505,30 @@
       <c r="M11"/>
       <c r="N11"/>
       <c r="O11"/>
-      <c r="P11" t="s">
-        <v>63</v>
-      </c>
+      <c r="P11"/>
       <c r="Q11"/>
       <c r="R11"/>
       <c r="S11"/>
       <c r="T11"/>
-      <c r="U11" t="s">
-        <v>64</v>
-      </c>
+      <c r="U11"/>
       <c r="V11"/>
       <c r="W11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
         <v>65</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12" t="s">
         <v>66</v>
       </c>
-      <c r="D12"/>
-      <c r="E12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12"/>
       <c r="G12"/>
       <c r="H12"/>
       <c r="I12"/>
@@ -1557,7 +1537,9 @@
       <c r="L12"/>
       <c r="M12"/>
       <c r="N12"/>
-      <c r="O12"/>
+      <c r="O12" t="s">
+        <v>67</v>
+      </c>
       <c r="P12"/>
       <c r="Q12"/>
       <c r="R12"/>
@@ -1569,7 +1551,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
         <v>68</v>
@@ -1579,20 +1561,20 @@
       </c>
       <c r="D13"/>
       <c r="E13"/>
-      <c r="F13" t="s">
-        <v>70</v>
-      </c>
+      <c r="F13"/>
       <c r="G13"/>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
-      <c r="L13"/>
-      <c r="M13"/>
+      <c r="L13" t="s">
+        <v>70</v>
+      </c>
+      <c r="M13" t="s">
+        <v>71</v>
+      </c>
       <c r="N13"/>
-      <c r="O13" t="s">
-        <v>71</v>
-      </c>
+      <c r="O13"/>
       <c r="P13"/>
       <c r="Q13"/>
       <c r="R13"/>
@@ -1604,10 +1586,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
         <v>73</v>
@@ -1620,17 +1602,15 @@
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
-      <c r="L14" t="s">
-        <v>74</v>
-      </c>
-      <c r="M14" t="s">
-        <v>75</v>
-      </c>
+      <c r="L14"/>
+      <c r="M14"/>
       <c r="N14"/>
       <c r="O14"/>
       <c r="P14"/>
       <c r="Q14"/>
-      <c r="R14"/>
+      <c r="R14" t="s">
+        <v>74</v>
+      </c>
       <c r="S14"/>
       <c r="T14"/>
       <c r="U14"/>
@@ -1639,17 +1619,19 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" t="s">
         <v>76</v>
-      </c>
-      <c r="B15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" t="s">
-        <v>77</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
-      <c r="F15"/>
+      <c r="F15" t="s">
+        <v>77</v>
+      </c>
       <c r="G15"/>
       <c r="H15"/>
       <c r="I15"/>
@@ -1661,18 +1643,18 @@
       <c r="O15"/>
       <c r="P15"/>
       <c r="Q15"/>
-      <c r="R15" t="s">
-        <v>78</v>
-      </c>
+      <c r="R15"/>
       <c r="S15"/>
       <c r="T15"/>
       <c r="U15"/>
       <c r="V15"/>
-      <c r="W15"/>
+      <c r="W15" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B16" t="s">
         <v>79</v>
@@ -1682,12 +1664,14 @@
       </c>
       <c r="D16"/>
       <c r="E16"/>
-      <c r="F16" t="s">
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16" t="s">
         <v>81</v>
       </c>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
+      <c r="I16" t="s">
+        <v>82</v>
+      </c>
       <c r="J16"/>
       <c r="K16"/>
       <c r="L16"/>
@@ -1697,37 +1681,37 @@
       <c r="P16"/>
       <c r="Q16"/>
       <c r="R16"/>
-      <c r="S16"/>
+      <c r="S16" t="s">
+        <v>83</v>
+      </c>
       <c r="T16"/>
       <c r="U16"/>
-      <c r="V16"/>
-      <c r="W16" t="s">
-        <v>82</v>
-      </c>
+      <c r="V16" t="s">
+        <v>84</v>
+      </c>
+      <c r="W16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
       <c r="F17"/>
       <c r="G17"/>
-      <c r="H17" t="s">
-        <v>85</v>
-      </c>
-      <c r="I17" t="s">
-        <v>86</v>
-      </c>
+      <c r="H17"/>
+      <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
-      <c r="L17"/>
+      <c r="L17" t="s">
+        <v>87</v>
+      </c>
       <c r="M17"/>
       <c r="N17"/>
       <c r="O17"/>
@@ -1735,24 +1719,24 @@
       <c r="Q17"/>
       <c r="R17"/>
       <c r="S17" t="s">
-        <v>87</v>
-      </c>
-      <c r="T17"/>
+        <v>88</v>
+      </c>
+      <c r="T17" t="s">
+        <v>89</v>
+      </c>
       <c r="U17"/>
-      <c r="V17" t="s">
-        <v>88</v>
-      </c>
+      <c r="V17"/>
       <c r="W17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -1760,54 +1744,54 @@
       <c r="G18"/>
       <c r="H18"/>
       <c r="I18"/>
-      <c r="J18"/>
+      <c r="J18" t="s">
+        <v>93</v>
+      </c>
       <c r="K18"/>
-      <c r="L18" t="s">
-        <v>91</v>
-      </c>
+      <c r="L18"/>
       <c r="M18"/>
       <c r="N18"/>
       <c r="O18"/>
       <c r="P18"/>
       <c r="Q18"/>
       <c r="R18"/>
-      <c r="S18" t="s">
-        <v>92</v>
-      </c>
-      <c r="T18" t="s">
-        <v>93</v>
-      </c>
+      <c r="S18"/>
+      <c r="T18"/>
       <c r="U18"/>
       <c r="V18"/>
       <c r="W18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" t="s">
         <v>94</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>95</v>
-      </c>
-      <c r="C19" t="s">
-        <v>96</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
       <c r="F19"/>
       <c r="G19"/>
-      <c r="H19"/>
+      <c r="H19" t="s">
+        <v>96</v>
+      </c>
       <c r="I19"/>
-      <c r="J19" t="s">
-        <v>97</v>
-      </c>
+      <c r="J19"/>
       <c r="K19"/>
       <c r="L19"/>
       <c r="M19"/>
       <c r="N19"/>
-      <c r="O19"/>
+      <c r="O19" t="s">
+        <v>97</v>
+      </c>
       <c r="P19"/>
       <c r="Q19"/>
-      <c r="R19"/>
+      <c r="R19" t="s">
+        <v>98</v>
+      </c>
       <c r="S19"/>
       <c r="T19"/>
       <c r="U19"/>
@@ -1816,50 +1800,50 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
       <c r="F20"/>
       <c r="G20"/>
-      <c r="H20" t="s">
-        <v>100</v>
-      </c>
+      <c r="H20"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
-      <c r="L20"/>
+      <c r="L20" t="s">
+        <v>101</v>
+      </c>
       <c r="M20"/>
       <c r="N20"/>
-      <c r="O20" t="s">
-        <v>101</v>
-      </c>
-      <c r="P20"/>
+      <c r="O20"/>
+      <c r="P20" t="s">
+        <v>102</v>
+      </c>
       <c r="Q20"/>
-      <c r="R20" t="s">
-        <v>102</v>
-      </c>
+      <c r="R20"/>
       <c r="S20"/>
-      <c r="T20"/>
+      <c r="T20" t="s">
+        <v>103</v>
+      </c>
       <c r="U20"/>
       <c r="V20"/>
       <c r="W20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -1869,9 +1853,7 @@
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
-      <c r="L21" t="s">
-        <v>105</v>
-      </c>
+      <c r="L21"/>
       <c r="M21"/>
       <c r="N21"/>
       <c r="O21"/>
@@ -1881,22 +1863,22 @@
       <c r="Q21"/>
       <c r="R21"/>
       <c r="S21"/>
-      <c r="T21" t="s">
+      <c r="T21"/>
+      <c r="U21" t="s">
         <v>107</v>
       </c>
-      <c r="U21"/>
       <c r="V21"/>
       <c r="W21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -1905,33 +1887,31 @@
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22"/>
-      <c r="K22"/>
+      <c r="K22" t="s">
+        <v>111</v>
+      </c>
       <c r="L22"/>
       <c r="M22"/>
       <c r="N22"/>
       <c r="O22"/>
-      <c r="P22" t="s">
-        <v>110</v>
-      </c>
+      <c r="P22"/>
       <c r="Q22"/>
       <c r="R22"/>
       <c r="S22"/>
       <c r="T22"/>
-      <c r="U22" t="s">
-        <v>111</v>
-      </c>
+      <c r="U22"/>
       <c r="V22"/>
       <c r="W22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" t="s">
         <v>112</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>113</v>
-      </c>
-      <c r="C23" t="s">
-        <v>114</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -1940,31 +1920,35 @@
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23"/>
-      <c r="K23" t="s">
-        <v>115</v>
-      </c>
+      <c r="K23"/>
       <c r="L23"/>
       <c r="M23"/>
-      <c r="N23"/>
+      <c r="N23" t="s">
+        <v>114</v>
+      </c>
       <c r="O23"/>
       <c r="P23"/>
       <c r="Q23"/>
       <c r="R23"/>
       <c r="S23"/>
-      <c r="T23"/>
-      <c r="U23"/>
+      <c r="T23" t="s">
+        <v>115</v>
+      </c>
+      <c r="U23" t="s">
+        <v>116</v>
+      </c>
       <c r="V23"/>
       <c r="W23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -1975,74 +1959,78 @@
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24"/>
-      <c r="M24"/>
-      <c r="N24" t="s">
-        <v>118</v>
-      </c>
+      <c r="M24" t="s">
+        <v>119</v>
+      </c>
+      <c r="N24"/>
       <c r="O24"/>
       <c r="P24"/>
       <c r="Q24"/>
       <c r="R24"/>
       <c r="S24"/>
-      <c r="T24" t="s">
-        <v>119</v>
-      </c>
-      <c r="U24" t="s">
-        <v>120</v>
-      </c>
+      <c r="T24"/>
+      <c r="U24"/>
       <c r="V24"/>
       <c r="W24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" t="s">
         <v>121</v>
-      </c>
-      <c r="C25" t="s">
-        <v>122</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
-      <c r="F25"/>
+      <c r="F25" t="s">
+        <v>122</v>
+      </c>
       <c r="G25"/>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25"/>
-      <c r="M25" t="s">
-        <v>123</v>
-      </c>
+      <c r="M25"/>
       <c r="N25"/>
       <c r="O25"/>
       <c r="P25"/>
       <c r="Q25"/>
-      <c r="R25"/>
+      <c r="R25" t="s">
+        <v>123</v>
+      </c>
       <c r="S25"/>
-      <c r="T25"/>
+      <c r="T25" t="s">
+        <v>124</v>
+      </c>
       <c r="U25"/>
-      <c r="V25"/>
+      <c r="V25" t="s">
+        <v>125</v>
+      </c>
       <c r="W25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
       <c r="F26" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G26"/>
-      <c r="H26"/>
+      <c r="H26" t="s">
+        <v>130</v>
+      </c>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2052,22 +2040,16 @@
       <c r="O26"/>
       <c r="P26"/>
       <c r="Q26"/>
-      <c r="R26" t="s">
-        <v>127</v>
-      </c>
+      <c r="R26"/>
       <c r="S26"/>
-      <c r="T26" t="s">
-        <v>128</v>
-      </c>
+      <c r="T26"/>
       <c r="U26"/>
-      <c r="V26" t="s">
-        <v>129</v>
-      </c>
+      <c r="V26"/>
       <c r="W26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B27" t="s">
         <v>131</v>
@@ -2075,25 +2057,29 @@
       <c r="C27" t="s">
         <v>132</v>
       </c>
-      <c r="D27"/>
+      <c r="D27" t="s">
+        <v>133</v>
+      </c>
       <c r="E27"/>
       <c r="F27" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G27"/>
-      <c r="H27" t="s">
-        <v>134</v>
-      </c>
+      <c r="H27"/>
       <c r="I27"/>
       <c r="J27"/>
-      <c r="K27"/>
+      <c r="K27" t="s">
+        <v>135</v>
+      </c>
       <c r="L27"/>
       <c r="M27"/>
       <c r="N27"/>
       <c r="O27"/>
       <c r="P27"/>
       <c r="Q27"/>
-      <c r="R27"/>
+      <c r="R27" t="s">
+        <v>136</v>
+      </c>
       <c r="S27"/>
       <c r="T27"/>
       <c r="U27"/>
@@ -2102,59 +2088,57 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C28" t="s">
-        <v>136</v>
-      </c>
-      <c r="D28" t="s">
-        <v>137</v>
-      </c>
-      <c r="E28"/>
-      <c r="F28" t="s">
         <v>138</v>
       </c>
+      <c r="D28"/>
+      <c r="E28" t="s">
+        <v>139</v>
+      </c>
+      <c r="F28"/>
       <c r="G28"/>
       <c r="H28"/>
       <c r="I28"/>
       <c r="J28"/>
-      <c r="K28" t="s">
-        <v>139</v>
-      </c>
+      <c r="K28"/>
       <c r="L28"/>
       <c r="M28"/>
       <c r="N28"/>
       <c r="O28"/>
       <c r="P28"/>
       <c r="Q28"/>
-      <c r="R28" t="s">
+      <c r="R28"/>
+      <c r="S28" t="s">
         <v>140</v>
       </c>
-      <c r="S28"/>
       <c r="T28"/>
       <c r="U28"/>
       <c r="V28"/>
-      <c r="W28"/>
+      <c r="W28" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D29"/>
-      <c r="E29" t="s">
-        <v>143</v>
-      </c>
+      <c r="E29"/>
       <c r="F29"/>
-      <c r="G29"/>
+      <c r="G29" t="s">
+        <v>144</v>
+      </c>
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29"/>
@@ -2164,9 +2148,7 @@
       <c r="N29"/>
       <c r="O29"/>
       <c r="P29"/>
-      <c r="Q29" t="s">
-        <v>144</v>
-      </c>
+      <c r="Q29"/>
       <c r="R29"/>
       <c r="S29" t="s">
         <v>145</v>
@@ -2174,13 +2156,11 @@
       <c r="T29"/>
       <c r="U29"/>
       <c r="V29"/>
-      <c r="W29" t="s">
-        <v>146</v>
-      </c>
+      <c r="W29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="B30" t="s">
         <v>147</v>
@@ -2191,9 +2171,7 @@
       <c r="D30"/>
       <c r="E30"/>
       <c r="F30"/>
-      <c r="G30" t="s">
-        <v>149</v>
-      </c>
+      <c r="G30"/>
       <c r="H30"/>
       <c r="I30"/>
       <c r="J30"/>
@@ -2206,7 +2184,7 @@
       <c r="Q30"/>
       <c r="R30"/>
       <c r="S30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="T30"/>
       <c r="U30"/>
@@ -2215,13 +2193,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" t="s">
+        <v>150</v>
+      </c>
+      <c r="C31" t="s">
         <v>151</v>
-      </c>
-      <c r="B31" t="s">
-        <v>152</v>
-      </c>
-      <c r="C31" t="s">
-        <v>153</v>
       </c>
       <c r="D31"/>
       <c r="E31"/>
@@ -2238,25 +2216,27 @@
       <c r="P31"/>
       <c r="Q31"/>
       <c r="R31"/>
-      <c r="S31" t="s">
-        <v>154</v>
-      </c>
-      <c r="T31"/>
+      <c r="S31"/>
+      <c r="T31" t="s">
+        <v>152</v>
+      </c>
       <c r="U31"/>
       <c r="V31"/>
       <c r="W31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B32" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D32" t="s">
         <v>155</v>
       </c>
-      <c r="C32" t="s">
-        <v>156</v>
-      </c>
-      <c r="D32"/>
       <c r="E32"/>
       <c r="F32"/>
       <c r="G32"/>
@@ -2272,25 +2252,25 @@
       <c r="Q32"/>
       <c r="R32"/>
       <c r="S32"/>
-      <c r="T32" t="s">
-        <v>157</v>
-      </c>
+      <c r="T32"/>
       <c r="U32"/>
       <c r="V32"/>
-      <c r="W32"/>
+      <c r="W32" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B33" t="s">
+        <v>157</v>
+      </c>
+      <c r="C33" t="s">
         <v>158</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>159</v>
-      </c>
-      <c r="D33" t="s">
-        <v>160</v>
       </c>
       <c r="E33"/>
       <c r="F33"/>
@@ -2299,7 +2279,9 @@
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
-      <c r="L33"/>
+      <c r="L33" t="s">
+        <v>160</v>
+      </c>
       <c r="M33"/>
       <c r="N33"/>
       <c r="O33"/>
@@ -2310,13 +2292,11 @@
       <c r="T33"/>
       <c r="U33"/>
       <c r="V33"/>
-      <c r="W33" t="s">
-        <v>161</v>
-      </c>
+      <c r="W33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B34" t="s">
         <v>162</v>
@@ -2324,88 +2304,88 @@
       <c r="C34" t="s">
         <v>163</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34" t="s">
         <v>164</v>
       </c>
-      <c r="E34"/>
-      <c r="F34"/>
       <c r="G34"/>
       <c r="H34"/>
-      <c r="I34"/>
+      <c r="I34" t="s">
+        <v>165</v>
+      </c>
       <c r="J34"/>
       <c r="K34"/>
-      <c r="L34" t="s">
-        <v>165</v>
-      </c>
+      <c r="L34"/>
       <c r="M34"/>
       <c r="N34"/>
       <c r="O34"/>
-      <c r="P34"/>
+      <c r="P34" t="s">
+        <v>166</v>
+      </c>
       <c r="Q34"/>
       <c r="R34"/>
       <c r="S34"/>
       <c r="T34"/>
       <c r="U34"/>
       <c r="V34"/>
-      <c r="W34"/>
+      <c r="W34" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B35" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C35" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D35"/>
       <c r="E35"/>
-      <c r="F35" t="s">
-        <v>169</v>
-      </c>
+      <c r="F35"/>
       <c r="G35"/>
       <c r="H35"/>
-      <c r="I35" t="s">
+      <c r="I35"/>
+      <c r="J35" t="s">
         <v>170</v>
       </c>
-      <c r="J35"/>
       <c r="K35"/>
       <c r="L35"/>
       <c r="M35"/>
       <c r="N35"/>
       <c r="O35"/>
-      <c r="P35" t="s">
-        <v>171</v>
-      </c>
+      <c r="P35"/>
       <c r="Q35"/>
       <c r="R35"/>
       <c r="S35"/>
       <c r="T35"/>
       <c r="U35"/>
       <c r="V35"/>
-      <c r="W35" t="s">
-        <v>172</v>
-      </c>
+      <c r="W35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B36" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C36" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D36"/>
       <c r="E36"/>
-      <c r="F36"/>
+      <c r="F36" t="s">
+        <v>173</v>
+      </c>
       <c r="G36"/>
       <c r="H36"/>
       <c r="I36"/>
       <c r="J36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K36"/>
       <c r="L36"/>
@@ -2414,9 +2394,7 @@
       <c r="O36"/>
       <c r="P36"/>
       <c r="Q36"/>
-      <c r="R36" t="s">
-        <v>176</v>
-      </c>
+      <c r="R36"/>
       <c r="S36"/>
       <c r="T36"/>
       <c r="U36"/>
@@ -2425,28 +2403,28 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B37" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C37" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D37"/>
       <c r="E37"/>
-      <c r="F37" t="s">
-        <v>179</v>
-      </c>
+      <c r="F37"/>
       <c r="G37"/>
       <c r="H37"/>
       <c r="I37"/>
-      <c r="J37" t="s">
-        <v>180</v>
-      </c>
+      <c r="J37"/>
       <c r="K37"/>
-      <c r="L37"/>
-      <c r="M37"/>
+      <c r="L37" t="s">
+        <v>177</v>
+      </c>
+      <c r="M37" t="s">
+        <v>178</v>
+      </c>
       <c r="N37"/>
       <c r="O37"/>
       <c r="P37"/>
@@ -2454,13 +2432,15 @@
       <c r="R37"/>
       <c r="S37"/>
       <c r="T37"/>
-      <c r="U37"/>
+      <c r="U37" t="s">
+        <v>179</v>
+      </c>
       <c r="V37"/>
       <c r="W37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="B38" t="s">
         <v>181</v>
@@ -2468,55 +2448,57 @@
       <c r="C38" t="s">
         <v>182</v>
       </c>
-      <c r="D38" t="s">
-        <v>183</v>
-      </c>
+      <c r="D38"/>
       <c r="E38"/>
       <c r="F38"/>
       <c r="G38"/>
-      <c r="H38"/>
+      <c r="H38" t="s">
+        <v>183</v>
+      </c>
       <c r="I38"/>
       <c r="J38"/>
       <c r="K38"/>
       <c r="L38" t="s">
         <v>184</v>
       </c>
-      <c r="M38" t="s">
-        <v>185</v>
-      </c>
+      <c r="M38"/>
       <c r="N38"/>
       <c r="O38"/>
       <c r="P38"/>
       <c r="Q38"/>
-      <c r="R38"/>
+      <c r="R38" t="s">
+        <v>185</v>
+      </c>
       <c r="S38"/>
-      <c r="T38"/>
-      <c r="U38" t="s">
+      <c r="T38" t="s">
         <v>186</v>
       </c>
+      <c r="U38"/>
       <c r="V38"/>
       <c r="W38"/>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>180</v>
+      </c>
+      <c r="B39" t="s">
         <v>187</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>188</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39"/>
+      <c r="E39" t="s">
         <v>189</v>
       </c>
-      <c r="D39"/>
-      <c r="E39"/>
       <c r="F39"/>
       <c r="G39"/>
-      <c r="H39" t="s">
-        <v>190</v>
-      </c>
+      <c r="H39"/>
       <c r="I39"/>
       <c r="J39"/>
-      <c r="K39"/>
+      <c r="K39" t="s">
+        <v>190</v>
+      </c>
       <c r="L39" t="s">
         <v>191</v>
       </c>
@@ -2524,21 +2506,21 @@
       <c r="N39"/>
       <c r="O39"/>
       <c r="P39"/>
-      <c r="Q39"/>
-      <c r="R39" t="s">
+      <c r="Q39" t="s">
         <v>192</v>
       </c>
-      <c r="S39"/>
-      <c r="T39" t="s">
+      <c r="R39"/>
+      <c r="S39" t="s">
         <v>193</v>
       </c>
+      <c r="T39"/>
       <c r="U39"/>
       <c r="V39"/>
       <c r="W39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B40" t="s">
         <v>194</v>
@@ -2547,47 +2529,43 @@
         <v>195</v>
       </c>
       <c r="D40"/>
-      <c r="E40" t="s">
-        <v>196</v>
-      </c>
-      <c r="F40" t="s">
-        <v>197</v>
-      </c>
+      <c r="E40"/>
+      <c r="F40"/>
       <c r="G40"/>
       <c r="H40"/>
       <c r="I40"/>
       <c r="J40"/>
-      <c r="K40" t="s">
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40" t="s">
+        <v>196</v>
+      </c>
+      <c r="O40" t="s">
+        <v>197</v>
+      </c>
+      <c r="P40"/>
+      <c r="Q40"/>
+      <c r="R40"/>
+      <c r="S40"/>
+      <c r="T40"/>
+      <c r="U40" t="s">
         <v>198</v>
       </c>
-      <c r="L40" t="s">
+      <c r="V40" t="s">
         <v>199</v>
       </c>
-      <c r="M40"/>
-      <c r="N40"/>
-      <c r="O40"/>
-      <c r="P40"/>
-      <c r="Q40" t="s">
-        <v>200</v>
-      </c>
-      <c r="R40"/>
-      <c r="S40" t="s">
-        <v>201</v>
-      </c>
-      <c r="T40"/>
-      <c r="U40"/>
-      <c r="V40"/>
       <c r="W40"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D41"/>
       <c r="E41"/>
@@ -2598,44 +2576,42 @@
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41"/>
-      <c r="M41" t="s">
-        <v>204</v>
-      </c>
-      <c r="N41" t="s">
-        <v>205</v>
-      </c>
-      <c r="O41" t="s">
-        <v>206</v>
-      </c>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
       <c r="P41"/>
       <c r="Q41"/>
       <c r="R41"/>
       <c r="S41"/>
-      <c r="T41"/>
-      <c r="U41" t="s">
-        <v>207</v>
-      </c>
-      <c r="V41" t="s">
-        <v>208</v>
-      </c>
+      <c r="T41" t="s">
+        <v>202</v>
+      </c>
+      <c r="U41"/>
+      <c r="V41"/>
       <c r="W41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C42" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D42"/>
       <c r="E42"/>
       <c r="F42"/>
-      <c r="G42"/>
-      <c r="H42"/>
-      <c r="I42"/>
+      <c r="G42" t="s">
+        <v>206</v>
+      </c>
+      <c r="H42" t="s">
+        <v>207</v>
+      </c>
+      <c r="I42" t="s">
+        <v>208</v>
+      </c>
       <c r="J42"/>
       <c r="K42"/>
       <c r="L42"/>
@@ -2646,82 +2622,74 @@
       <c r="Q42"/>
       <c r="R42"/>
       <c r="S42"/>
-      <c r="T42" t="s">
-        <v>211</v>
-      </c>
+      <c r="T42"/>
       <c r="U42"/>
-      <c r="V42"/>
+      <c r="V42" t="s">
+        <v>209</v>
+      </c>
       <c r="W42"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B43" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C43" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D43"/>
       <c r="E43"/>
       <c r="F43"/>
-      <c r="G43" t="s">
-        <v>215</v>
-      </c>
-      <c r="H43" t="s">
-        <v>216</v>
-      </c>
-      <c r="I43" t="s">
-        <v>217</v>
-      </c>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43"/>
       <c r="J43"/>
       <c r="K43"/>
       <c r="L43"/>
       <c r="M43"/>
-      <c r="N43"/>
-      <c r="O43"/>
+      <c r="N43" t="s">
+        <v>212</v>
+      </c>
+      <c r="O43" t="s">
+        <v>213</v>
+      </c>
       <c r="P43"/>
-      <c r="Q43" t="s">
-        <v>218</v>
-      </c>
+      <c r="Q43"/>
       <c r="R43"/>
       <c r="S43"/>
       <c r="T43"/>
       <c r="U43"/>
-      <c r="V43" t="s">
-        <v>219</v>
-      </c>
+      <c r="V43"/>
       <c r="W43"/>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B44" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C44" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D44"/>
       <c r="E44"/>
-      <c r="F44"/>
+      <c r="F44" t="s">
+        <v>216</v>
+      </c>
       <c r="G44"/>
       <c r="H44" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="I44"/>
       <c r="J44"/>
       <c r="K44"/>
       <c r="L44"/>
       <c r="M44"/>
-      <c r="N44" t="s">
-        <v>223</v>
-      </c>
-      <c r="O44" t="s">
-        <v>224</v>
-      </c>
+      <c r="N44"/>
+      <c r="O44"/>
       <c r="P44"/>
       <c r="Q44"/>
       <c r="R44"/>
@@ -2733,23 +2701,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B45" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C45" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D45"/>
       <c r="E45"/>
       <c r="F45" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G45"/>
-      <c r="H45" t="s">
-        <v>228</v>
-      </c>
+      <c r="H45"/>
       <c r="I45"/>
       <c r="J45"/>
       <c r="K45"/>
@@ -2768,105 +2734,107 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B46" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C46" t="s">
-        <v>230</v>
-      </c>
-      <c r="D46"/>
-      <c r="E46"/>
-      <c r="F46" t="s">
-        <v>231</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="D46" t="s">
+        <v>224</v>
+      </c>
+      <c r="E46" t="s">
+        <v>225</v>
+      </c>
+      <c r="F46"/>
       <c r="G46"/>
       <c r="H46"/>
       <c r="I46"/>
       <c r="J46"/>
       <c r="K46"/>
-      <c r="L46"/>
+      <c r="L46" t="s">
+        <v>226</v>
+      </c>
       <c r="M46"/>
-      <c r="N46"/>
-      <c r="O46"/>
+      <c r="N46" t="s">
+        <v>227</v>
+      </c>
+      <c r="O46" t="s">
+        <v>228</v>
+      </c>
       <c r="P46"/>
       <c r="Q46"/>
       <c r="R46"/>
-      <c r="S46"/>
+      <c r="S46" t="s">
+        <v>229</v>
+      </c>
       <c r="T46"/>
       <c r="U46"/>
-      <c r="V46"/>
+      <c r="V46" t="s">
+        <v>230</v>
+      </c>
       <c r="W46"/>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>221</v>
+      </c>
+      <c r="B47" t="s">
+        <v>231</v>
+      </c>
+      <c r="C47" t="s">
         <v>232</v>
       </c>
-      <c r="B47" t="s">
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47" t="s">
         <v>233</v>
       </c>
-      <c r="C47" t="s">
-        <v>234</v>
-      </c>
-      <c r="D47" t="s">
-        <v>235</v>
-      </c>
-      <c r="E47" t="s">
-        <v>236</v>
-      </c>
-      <c r="F47"/>
-      <c r="G47"/>
       <c r="H47"/>
       <c r="I47"/>
       <c r="J47"/>
       <c r="K47"/>
-      <c r="L47" t="s">
-        <v>237</v>
-      </c>
+      <c r="L47"/>
       <c r="M47"/>
-      <c r="N47" t="s">
-        <v>238</v>
-      </c>
-      <c r="O47" t="s">
-        <v>239</v>
-      </c>
+      <c r="N47"/>
+      <c r="O47"/>
       <c r="P47"/>
       <c r="Q47"/>
       <c r="R47"/>
-      <c r="S47" t="s">
-        <v>240</v>
-      </c>
+      <c r="S47"/>
       <c r="T47"/>
       <c r="U47"/>
-      <c r="V47" t="s">
-        <v>241</v>
-      </c>
+      <c r="V47"/>
       <c r="W47"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B48" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C48" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D48"/>
       <c r="E48"/>
       <c r="F48"/>
-      <c r="G48" t="s">
-        <v>244</v>
-      </c>
-      <c r="H48"/>
+      <c r="G48"/>
+      <c r="H48" t="s">
+        <v>236</v>
+      </c>
       <c r="I48"/>
       <c r="J48"/>
       <c r="K48"/>
       <c r="L48"/>
       <c r="M48"/>
-      <c r="N48"/>
+      <c r="N48" t="s">
+        <v>237</v>
+      </c>
       <c r="O48"/>
       <c r="P48"/>
       <c r="Q48"/>
@@ -2879,112 +2847,44 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B49" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C49" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D49"/>
       <c r="E49"/>
       <c r="F49"/>
       <c r="G49"/>
-      <c r="H49" t="s">
-        <v>247</v>
-      </c>
-      <c r="I49"/>
+      <c r="H49"/>
+      <c r="I49" t="s">
+        <v>240</v>
+      </c>
       <c r="J49"/>
-      <c r="K49"/>
+      <c r="K49" t="s">
+        <v>241</v>
+      </c>
       <c r="L49"/>
       <c r="M49"/>
       <c r="N49" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="O49"/>
-      <c r="P49"/>
+      <c r="P49" t="s">
+        <v>243</v>
+      </c>
       <c r="Q49"/>
       <c r="R49"/>
-      <c r="S49"/>
+      <c r="S49" t="s">
+        <v>244</v>
+      </c>
       <c r="T49"/>
       <c r="U49"/>
       <c r="V49"/>
       <c r="W49"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>232</v>
-      </c>
-      <c r="B50" t="s">
-        <v>249</v>
-      </c>
-      <c r="C50" t="s">
-        <v>250</v>
-      </c>
-      <c r="D50"/>
-      <c r="E50"/>
-      <c r="F50"/>
-      <c r="G50"/>
-      <c r="H50"/>
-      <c r="I50" t="s">
-        <v>251</v>
-      </c>
-      <c r="J50"/>
-      <c r="K50" t="s">
-        <v>252</v>
-      </c>
-      <c r="L50"/>
-      <c r="M50"/>
-      <c r="N50" t="s">
-        <v>253</v>
-      </c>
-      <c r="O50"/>
-      <c r="P50" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q50"/>
-      <c r="R50"/>
-      <c r="S50" t="s">
-        <v>255</v>
-      </c>
-      <c r="T50"/>
-      <c r="U50"/>
-      <c r="V50"/>
-      <c r="W50"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>23</v>
-      </c>
-      <c r="B51" t="s">
-        <v>256</v>
-      </c>
-      <c r="C51" t="s">
-        <v>23</v>
-      </c>
-      <c r="D51"/>
-      <c r="E51"/>
-      <c r="F51"/>
-      <c r="G51"/>
-      <c r="H51"/>
-      <c r="I51"/>
-      <c r="J51"/>
-      <c r="K51"/>
-      <c r="L51"/>
-      <c r="M51"/>
-      <c r="N51"/>
-      <c r="O51"/>
-      <c r="P51"/>
-      <c r="Q51" t="s">
-        <v>257</v>
-      </c>
-      <c r="R51"/>
-      <c r="S51"/>
-      <c r="T51"/>
-      <c r="U51"/>
-      <c r="V51"/>
-      <c r="W51"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2998,73 +2898,73 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3088,7 +2988,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -3157,10 +3057,10 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -3202,10 +3102,10 @@
         <v>26</v>
       </c>
       <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
         <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>38</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -3247,10 +3147,10 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>245</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>246</v>
       </c>
       <c r="D6"/>
       <c r="E6" t="n">
@@ -3291,13 +3191,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D7"/>
       <c r="E7" t="n">
@@ -3340,13 +3240,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -3380,20 +3280,18 @@
       </c>
       <c r="T8"/>
       <c r="U8"/>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
+      <c r="V8"/>
       <c r="W8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -3432,13 +3330,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -3475,13 +3373,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -3499,7 +3397,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N11"/>
       <c r="O11"/>
@@ -3518,13 +3416,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -3567,13 +3465,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -3624,13 +3522,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -3644,19 +3542,13 @@
       <c r="I14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
+      <c r="J14"/>
       <c r="K14"/>
       <c r="L14"/>
       <c r="M14"/>
       <c r="N14"/>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
+      <c r="O14"/>
+      <c r="P14"/>
       <c r="Q14"/>
       <c r="R14" t="n">
         <v>1</v>
@@ -3675,13 +3567,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -3728,13 +3620,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" t="s">
         <v>76</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>80</v>
       </c>
       <c r="D16" t="n">
         <v>4</v>
@@ -3763,21 +3655,19 @@
       <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
+      <c r="U16"/>
       <c r="V16"/>
       <c r="W16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D17" t="n">
         <v>4</v>
@@ -3814,13 +3704,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D18"/>
       <c r="E18" t="n">
@@ -3863,13 +3753,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -3916,13 +3806,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
         <v>94</v>
       </c>
-      <c r="B20" t="s">
-        <v>98</v>
-      </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D20"/>
       <c r="E20" t="n">
@@ -3961,13 +3851,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4012,13 +3902,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -4065,13 +3955,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B23" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -4114,13 +4004,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" t="s">
         <v>112</v>
       </c>
-      <c r="B24" t="s">
-        <v>116</v>
-      </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -4141,9 +4031,7 @@
       <c r="L24"/>
       <c r="M24"/>
       <c r="N24"/>
-      <c r="O24" t="n">
-        <v>1</v>
-      </c>
+      <c r="O24"/>
       <c r="P24"/>
       <c r="Q24" t="n">
         <v>1</v>
@@ -4163,13 +4051,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -4206,19 +4094,17 @@
         <v>2</v>
       </c>
       <c r="V25"/>
-      <c r="W25" t="n">
-        <v>1</v>
-      </c>
+      <c r="W25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
@@ -4255,13 +4141,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B27" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D27" t="n">
         <v>2</v>
@@ -4300,13 +4186,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C28" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -4345,13 +4231,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B29" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C29" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
@@ -4386,19 +4272,19 @@
         <v>1</v>
       </c>
       <c r="V29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C30" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
@@ -4445,13 +4331,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B31" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C31" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D31"/>
       <c r="E31" t="n">
@@ -4486,13 +4372,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>146</v>
+      </c>
+      <c r="B32" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" t="s">
         <v>151</v>
-      </c>
-      <c r="B32" t="s">
-        <v>155</v>
-      </c>
-      <c r="C32" t="s">
-        <v>156</v>
       </c>
       <c r="D32"/>
       <c r="E32" t="n">
@@ -4539,13 +4425,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B33" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C33" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D33"/>
       <c r="E33" t="n">
@@ -4592,13 +4478,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B34" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C34" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D34"/>
       <c r="E34" t="n">
@@ -4641,13 +4527,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B35" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C35" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D35"/>
       <c r="E35"/>
@@ -4674,13 +4560,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B36" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C36" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D36"/>
       <c r="E36"/>
@@ -4719,13 +4605,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B37" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C37" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
@@ -4774,13 +4660,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B38" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C38" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D38"/>
       <c r="E38"/>
@@ -4813,13 +4699,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B39" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C39" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D39"/>
       <c r="E39" t="n">
@@ -4854,13 +4740,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>180</v>
+      </c>
+      <c r="B40" t="s">
         <v>187</v>
       </c>
-      <c r="B40" t="s">
-        <v>194</v>
-      </c>
       <c r="C40" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D40"/>
       <c r="E40"/>
@@ -4899,13 +4785,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B41" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C41" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D41" t="n">
         <v>2</v>
@@ -4946,13 +4832,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B42" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="C42" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
@@ -4995,13 +4881,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B43" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C43" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
@@ -5013,15 +4899,9 @@
       <c r="G43"/>
       <c r="H43"/>
       <c r="I43"/>
-      <c r="J43" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1</v>
-      </c>
+      <c r="J43"/>
+      <c r="K43"/>
+      <c r="L43"/>
       <c r="M43" t="n">
         <v>1</v>
       </c>
@@ -5044,13 +4924,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B44" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C44" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="D44"/>
       <c r="E44" t="n">
@@ -5091,13 +4971,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B45" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C45" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="D45"/>
       <c r="E45"/>
@@ -5142,13 +5022,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B46" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="C46" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D46"/>
       <c r="E46"/>
@@ -5187,13 +5067,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B47" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="C47" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="D47"/>
       <c r="E47"/>
@@ -5222,13 +5102,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>221</v>
+      </c>
+      <c r="B48" t="s">
+        <v>231</v>
+      </c>
+      <c r="C48" t="s">
         <v>232</v>
-      </c>
-      <c r="B48" t="s">
-        <v>242</v>
-      </c>
-      <c r="C48" t="s">
-        <v>243</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
@@ -5267,13 +5147,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B49" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="C49" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="D49" t="n">
         <v>1</v>
@@ -5310,13 +5190,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B50" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C50" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="D50" t="n">
         <v>2</v>
@@ -5358,7 +5238,7 @@
         <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C51" t="s">
         <v>23</v>

--- a/fifa_2026_sticker_trade.xlsx
+++ b/fifa_2026_sticker_trade.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="227">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -117,9 +117,6 @@
     <t xml:space="preserve">RSA</t>
   </si>
   <si>
-    <t xml:space="preserve">RSA_4</t>
-  </si>
-  <si>
     <t xml:space="preserve">RSA_7</t>
   </si>
   <si>
@@ -522,12 +519,6 @@
     <t xml:space="preserve">NOR_9</t>
   </si>
   <si>
-    <t xml:space="preserve">NOR_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOR_18</t>
-  </si>
-  <si>
     <t xml:space="preserve">J</t>
   </si>
   <si>
@@ -567,9 +558,6 @@
     <t xml:space="preserve">ALG_14</t>
   </si>
   <si>
-    <t xml:space="preserve">ALG_16</t>
-  </si>
-  <si>
     <t xml:space="preserve">Austria</t>
   </si>
   <si>
@@ -624,100 +612,85 @@
     <t xml:space="preserve">COD_11</t>
   </si>
   <si>
-    <t xml:space="preserve">COD_12</t>
+    <t xml:space="preserve">Colombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">England</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croatia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRO_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GHA_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CZE</t>
   </si>
   <si>
     <t xml:space="preserve">Uzbekistan</t>
   </si>
   <si>
     <t xml:space="preserve">UZB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UZB_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colombia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">England</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Croatia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRO_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GHA_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CZE</t>
   </si>
   <si>
     <t xml:space="preserve">World Cup Champions</t>
@@ -1225,13 +1198,11 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -1252,10 +1223,10 @@
         <v>26</v>
       </c>
       <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
         <v>36</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -1267,7 +1238,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1282,13 +1253,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
         <v>39</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>40</v>
-      </c>
-      <c r="C6" t="s">
-        <v>41</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -1296,7 +1267,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1315,17 +1286,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
         <v>43</v>
-      </c>
-      <c r="C7" t="s">
-        <v>44</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -1336,7 +1307,7 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
@@ -1350,13 +1321,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
         <v>47</v>
-      </c>
-      <c r="C8" t="s">
-        <v>48</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -1372,11 +1343,11 @@
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R8" s="2"/>
       <c r="S8" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
@@ -1385,13 +1356,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
         <v>51</v>
-      </c>
-      <c r="C9" t="s">
-        <v>52</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -1404,7 +1375,7 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
@@ -1418,18 +1389,18 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
         <v>54</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>56</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -1441,31 +1412,31 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
         <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>61</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -1488,18 +1459,18 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
         <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>64</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -1510,7 +1481,7 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
@@ -1523,13 +1494,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
         <v>67</v>
-      </c>
-      <c r="C13" t="s">
-        <v>68</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -1540,10 +1511,10 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M13" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -1558,13 +1529,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s">
         <v>71</v>
       </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -1581,7 +1552,7 @@
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
@@ -1591,18 +1562,18 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
         <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>75</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -1621,28 +1592,28 @@
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
       <c r="W15" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" t="s">
         <v>78</v>
-      </c>
-      <c r="C16" t="s">
-        <v>79</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -1657,19 +1628,19 @@
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
       <c r="V16" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="W16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" t="s">
         <v>83</v>
-      </c>
-      <c r="C17" t="s">
-        <v>84</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -1680,7 +1651,7 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -1689,10 +1660,10 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
       <c r="S17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="T17" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
@@ -1700,13 +1671,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" t="s">
         <v>88</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>89</v>
-      </c>
-      <c r="C18" t="s">
-        <v>90</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -1715,7 +1686,7 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
@@ -1733,20 +1704,20 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s">
         <v>92</v>
-      </c>
-      <c r="C19" t="s">
-        <v>93</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -1755,12 +1726,12 @@
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
@@ -1770,13 +1741,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" t="s">
         <v>97</v>
-      </c>
-      <c r="C20" t="s">
-        <v>98</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -1791,13 +1762,13 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
@@ -1805,13 +1776,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" t="s">
         <v>101</v>
-      </c>
-      <c r="C21" t="s">
-        <v>102</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -1826,7 +1797,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
@@ -1838,13 +1809,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" t="s">
         <v>104</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>105</v>
-      </c>
-      <c r="C22" t="s">
-        <v>106</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -1854,7 +1825,7 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -1871,13 +1842,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" t="s">
         <v>108</v>
-      </c>
-      <c r="C23" t="s">
-        <v>109</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -1890,7 +1861,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -1898,7 +1869,7 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
@@ -1906,13 +1877,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" t="s">
         <v>112</v>
-      </c>
-      <c r="C24" t="s">
-        <v>113</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -1924,7 +1895,7 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -1939,18 +1910,18 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" t="s">
         <v>115</v>
-      </c>
-      <c r="C25" t="s">
-        <v>116</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -1964,36 +1935,36 @@
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S25" s="2"/>
       <c r="T25" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U25" s="2"/>
       <c r="V25" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" t="s">
         <v>121</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>122</v>
-      </c>
-      <c r="C26" t="s">
-        <v>123</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
@@ -2013,27 +1984,27 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B27" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" t="s">
         <v>126</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -2042,7 +2013,7 @@
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
       <c r="R27" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
@@ -2052,17 +2023,17 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" t="s">
         <v>132</v>
-      </c>
-      <c r="C28" t="s">
-        <v>133</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -2078,30 +2049,30 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
       <c r="S28" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
       <c r="W28" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B29" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" t="s">
         <v>137</v>
-      </c>
-      <c r="C29" t="s">
-        <v>138</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -2122,13 +2093,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>139</v>
+      </c>
+      <c r="B30" t="s">
         <v>140</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>141</v>
-      </c>
-      <c r="C30" t="s">
-        <v>142</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -2146,7 +2117,7 @@
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
       <c r="S30" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
@@ -2155,13 +2126,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B31" t="s">
+        <v>143</v>
+      </c>
+      <c r="C31" t="s">
         <v>144</v>
-      </c>
-      <c r="C31" t="s">
-        <v>145</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -2180,7 +2151,7 @@
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
       <c r="T31" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
@@ -2188,16 +2159,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B32" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" t="s">
         <v>147</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -2218,21 +2189,21 @@
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
       <c r="W32" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B33" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" t="s">
         <v>151</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -2242,7 +2213,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -2258,18 +2229,18 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>154</v>
+      </c>
+      <c r="B34" t="s">
         <v>155</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>156</v>
-      </c>
-      <c r="C34" t="s">
-        <v>157</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -2281,7 +2252,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
@@ -2293,13 +2264,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B35" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" t="s">
         <v>160</v>
-      </c>
-      <c r="C35" t="s">
-        <v>161</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -2308,7 +2279,7 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
@@ -2326,13 +2297,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B36" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" t="s">
         <v>163</v>
-      </c>
-      <c r="C36" t="s">
-        <v>164</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -2341,7 +2312,7 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
@@ -2359,13 +2330,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B37" t="s">
+        <v>165</v>
+      </c>
+      <c r="C37" t="s">
         <v>166</v>
-      </c>
-      <c r="C37" t="s">
-        <v>167</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -2376,11 +2347,9 @@
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>169</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -2388,34 +2357,32 @@
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
       <c r="T37" s="2"/>
-      <c r="U37" s="2" t="s">
-        <v>170</v>
-      </c>
+      <c r="U37" s="2"/>
       <c r="V37" s="2"/>
       <c r="W37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C38" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -2423,11 +2390,11 @@
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="S38" s="2"/>
       <c r="T38" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="U38" s="2"/>
       <c r="V38" s="2"/>
@@ -2435,17 +2402,17 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B39" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C39" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -2453,22 +2420,20 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
       <c r="Q39" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="R39" s="2"/>
-      <c r="S39" s="2" t="s">
-        <v>184</v>
-      </c>
+      <c r="S39" s="2"/>
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
       <c r="V39" s="2"/>
@@ -2476,13 +2441,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B40" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C40" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
@@ -2495,10 +2460,10 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
@@ -2506,22 +2471,22 @@
       <c r="S40" s="2"/>
       <c r="T40" s="2"/>
       <c r="U40" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="W40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B41" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C41" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
@@ -2540,7 +2505,7 @@
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
       <c r="T41" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="U41" s="2"/>
       <c r="V41" s="2"/>
@@ -2548,23 +2513,23 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B42" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C42" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -2579,19 +2544,19 @@
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
       <c r="V42" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="W42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B43" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C43" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -2604,11 +2569,9 @@
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="O43" s="2" t="s">
-        <v>203</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" s="2"/>
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
@@ -2620,18 +2583,18 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B44" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C44" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -2653,19 +2616,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B45" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C45" t="s">
-        <v>208</v>
-      </c>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2" t="s">
-        <v>209</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
@@ -2673,85 +2638,79 @@
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="N45" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>208</v>
+      </c>
       <c r="P45" s="2"/>
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
       <c r="S45" s="2"/>
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
-      <c r="V45" s="2"/>
+      <c r="V45" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="W45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>202</v>
+      </c>
+      <c r="B46" t="s">
         <v>210</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>211</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
-      <c r="L46" s="2" t="s">
-        <v>215</v>
-      </c>
+      <c r="L46" s="2"/>
       <c r="M46" s="2"/>
-      <c r="N46" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="O46" s="2" t="s">
-        <v>217</v>
-      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" s="2"/>
       <c r="Q46" s="2"/>
       <c r="R46" s="2"/>
-      <c r="S46" s="2" t="s">
-        <v>218</v>
-      </c>
+      <c r="S46" s="2"/>
       <c r="T46" s="2"/>
       <c r="U46" s="2"/>
-      <c r="V46" s="2" t="s">
-        <v>219</v>
-      </c>
+      <c r="V46" s="2"/>
       <c r="W46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B47" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C47" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
-      <c r="N47" s="2"/>
+      <c r="N47" s="2" t="s">
+        <v>215</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
       <c r="Q47" s="2"/>
@@ -2764,77 +2723,42 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B48" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C48" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
+      <c r="I48" s="2" t="s">
+        <v>218</v>
+      </c>
       <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
+      <c r="K48" s="2" t="s">
+        <v>219</v>
+      </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
       <c r="R48" s="2"/>
-      <c r="S48" s="2"/>
+      <c r="S48" s="2" t="s">
+        <v>221</v>
+      </c>
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
       <c r="V48" s="2"/>
       <c r="W48" s="2"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>210</v>
-      </c>
-      <c r="B49" t="s">
-        <v>226</v>
-      </c>
-      <c r="C49" t="s">
-        <v>227</v>
-      </c>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="O49" s="2"/>
-      <c r="P49" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" s="2"/>
-      <c r="S49" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="T49" s="2"/>
-      <c r="U49" s="2"/>
-      <c r="V49" s="2"/>
-      <c r="W49" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3050,10 +2974,10 @@
         <v>26</v>
       </c>
       <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
         <v>36</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2</v>
@@ -3095,10 +3019,10 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="C6" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="n">
@@ -3139,13 +3063,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
         <v>39</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>40</v>
-      </c>
-      <c r="C7" t="s">
-        <v>41</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="n">
@@ -3186,13 +3110,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
         <v>43</v>
-      </c>
-      <c r="C8" t="s">
-        <v>44</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>1</v>
@@ -3231,13 +3155,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
         <v>47</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>1</v>
@@ -3276,13 +3200,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
         <v>51</v>
-      </c>
-      <c r="C10" t="s">
-        <v>52</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>1</v>
@@ -3319,13 +3243,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
         <v>54</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>55</v>
-      </c>
-      <c r="C11" t="s">
-        <v>56</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -3362,13 +3286,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
         <v>60</v>
-      </c>
-      <c r="C12" t="s">
-        <v>61</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -3411,13 +3335,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
         <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>64</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2</v>
@@ -3468,13 +3392,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
         <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>1</v>
@@ -3513,13 +3437,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" t="s">
         <v>71</v>
       </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>1</v>
@@ -3566,13 +3490,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
         <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>75</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>4</v>
@@ -3607,13 +3531,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
         <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>79</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>4</v>
@@ -3648,13 +3572,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" t="s">
         <v>83</v>
-      </c>
-      <c r="C18" t="s">
-        <v>84</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="n">
@@ -3697,13 +3621,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" t="s">
         <v>88</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>89</v>
-      </c>
-      <c r="C19" t="s">
-        <v>90</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>1</v>
@@ -3750,13 +3674,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
         <v>92</v>
-      </c>
-      <c r="C20" t="s">
-        <v>93</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="n">
@@ -3795,13 +3719,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" t="s">
         <v>97</v>
-      </c>
-      <c r="C21" t="s">
-        <v>98</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>1</v>
@@ -3844,13 +3768,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" t="s">
         <v>101</v>
-      </c>
-      <c r="C22" t="s">
-        <v>102</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>1</v>
@@ -3895,13 +3819,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" t="s">
         <v>104</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>105</v>
-      </c>
-      <c r="C23" t="s">
-        <v>106</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -3944,13 +3868,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" t="s">
         <v>108</v>
-      </c>
-      <c r="C24" t="s">
-        <v>109</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>3</v>
@@ -3989,13 +3913,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B25" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" t="s">
         <v>112</v>
-      </c>
-      <c r="C25" t="s">
-        <v>113</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -4036,13 +3960,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" t="s">
         <v>115</v>
-      </c>
-      <c r="C26" t="s">
-        <v>116</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>1</v>
@@ -4079,13 +4003,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" t="s">
         <v>121</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>122</v>
-      </c>
-      <c r="C27" t="s">
-        <v>123</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2</v>
@@ -4124,13 +4048,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" t="s">
         <v>126</v>
-      </c>
-      <c r="C28" t="s">
-        <v>127</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -4169,13 +4093,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B29" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" t="s">
         <v>132</v>
-      </c>
-      <c r="C29" t="s">
-        <v>133</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>1</v>
@@ -4216,13 +4140,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B30" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" t="s">
         <v>137</v>
-      </c>
-      <c r="C30" t="s">
-        <v>138</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>1</v>
@@ -4267,13 +4191,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" t="s">
         <v>140</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>141</v>
-      </c>
-      <c r="C31" t="s">
-        <v>142</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="n">
@@ -4308,13 +4232,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B32" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" t="s">
         <v>144</v>
-      </c>
-      <c r="C32" t="s">
-        <v>145</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2" t="n">
@@ -4361,13 +4285,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B33" t="s">
+        <v>146</v>
+      </c>
+      <c r="C33" t="s">
         <v>147</v>
-      </c>
-      <c r="C33" t="s">
-        <v>148</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2" t="n">
@@ -4414,13 +4338,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B34" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" t="s">
         <v>151</v>
-      </c>
-      <c r="C34" t="s">
-        <v>152</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2" t="n">
@@ -4463,13 +4387,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B35" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" t="s">
         <v>160</v>
-      </c>
-      <c r="C35" t="s">
-        <v>161</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -4508,13 +4432,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B36" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" t="s">
         <v>163</v>
-      </c>
-      <c r="C36" t="s">
-        <v>164</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>1</v>
@@ -4561,13 +4485,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B37" t="s">
+        <v>165</v>
+      </c>
+      <c r="C37" t="s">
         <v>166</v>
-      </c>
-      <c r="C37" t="s">
-        <v>167</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -4600,13 +4524,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C38" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2" t="n">
@@ -4641,13 +4565,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B39" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C39" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -4686,13 +4610,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B40" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C40" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>2</v>
@@ -4733,13 +4657,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B41" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C41" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>1</v>
@@ -4782,13 +4706,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B42" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C42" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>1</v>
@@ -4823,13 +4747,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B43" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C43" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2" t="n">
@@ -4870,13 +4794,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B44" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="C44" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
@@ -4919,13 +4843,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B45" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C45" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -4964,13 +4888,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B46" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C46" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
@@ -4999,13 +4923,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>202</v>
+      </c>
+      <c r="B47" t="s">
         <v>210</v>
       </c>
-      <c r="B47" t="s">
-        <v>220</v>
-      </c>
       <c r="C47" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>1</v>
@@ -5044,13 +4968,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B48" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C48" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>1</v>
@@ -5085,13 +5009,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B49" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C49" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>2</v>
@@ -5133,7 +5057,7 @@
         <v>23</v>
       </c>
       <c r="B50" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C50" t="s">
         <v>23</v>

--- a/fifa_2026_sticker_trade.xlsx
+++ b/fifa_2026_sticker_trade.xlsx
@@ -87,7 +87,10 @@
     <t xml:space="preserve">-</t>
   </si>
   <si>
-    <t xml:space="preserve">Intro</t>
+    <t xml:space="preserve">Special</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FWC</t>
   </si>
   <si>
     <t xml:space="preserve">FWC_7</t>
@@ -691,9 +694,6 @@
   </si>
   <si>
     <t xml:space="preserve">UZB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">World Cup Champions</t>
   </si>
 </sst>
 </file>
@@ -1123,7 +1123,7 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -1132,7 +1132,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -1150,27 +1150,27 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
@@ -1187,13 +1187,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -1202,7 +1202,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -1220,13 +1220,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -1238,7 +1238,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1253,13 +1253,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -1267,7 +1267,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1286,17 +1286,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -1307,7 +1307,7 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
@@ -1321,13 +1321,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -1343,11 +1343,11 @@
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R8" s="2"/>
       <c r="S8" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
@@ -1356,13 +1356,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -1375,7 +1375,7 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
@@ -1389,18 +1389,18 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -1412,31 +1412,31 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -1459,18 +1459,18 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -1481,7 +1481,7 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
@@ -1494,13 +1494,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -1511,10 +1511,10 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -1529,13 +1529,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -1552,7 +1552,7 @@
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
@@ -1562,18 +1562,18 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -1592,28 +1592,28 @@
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
       <c r="W15" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -1628,19 +1628,19 @@
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
       <c r="V16" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -1651,7 +1651,7 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -1660,10 +1660,10 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
       <c r="S17" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
@@ -1671,13 +1671,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -1686,7 +1686,7 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
@@ -1704,20 +1704,20 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -1726,12 +1726,12 @@
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
@@ -1741,13 +1741,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -1762,13 +1762,13 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
@@ -1776,13 +1776,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -1797,7 +1797,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
@@ -1809,13 +1809,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -1825,7 +1825,7 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -1842,13 +1842,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -1861,7 +1861,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -1869,7 +1869,7 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
@@ -1877,13 +1877,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -1895,7 +1895,7 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -1910,18 +1910,18 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -1935,36 +1935,36 @@
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S25" s="2"/>
       <c r="T25" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="U25" s="2"/>
       <c r="V25" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
@@ -1984,27 +1984,27 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -2013,7 +2013,7 @@
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
       <c r="R27" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
@@ -2023,17 +2023,17 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -2049,30 +2049,30 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
       <c r="S28" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
       <c r="W28" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C30" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -2117,7 +2117,7 @@
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
       <c r="S30" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
@@ -2126,13 +2126,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -2151,7 +2151,7 @@
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
       <c r="T31" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
@@ -2159,16 +2159,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B32" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -2189,21 +2189,21 @@
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
       <c r="W32" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -2213,7 +2213,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -2229,18 +2229,18 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B34" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -2252,7 +2252,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
@@ -2264,13 +2264,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C35" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -2279,7 +2279,7 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B36" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -2312,7 +2312,7 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
@@ -2330,13 +2330,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B37" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C37" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -2347,7 +2347,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
@@ -2363,26 +2363,26 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C38" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -2390,11 +2390,11 @@
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="S38" s="2"/>
       <c r="T38" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U38" s="2"/>
       <c r="V38" s="2"/>
@@ -2402,17 +2402,17 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B39" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C39" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -2420,17 +2420,17 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
       <c r="Q39" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
@@ -2441,13 +2441,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B40" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
@@ -2460,10 +2460,10 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
@@ -2471,22 +2471,22 @@
       <c r="S40" s="2"/>
       <c r="T40" s="2"/>
       <c r="U40" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="W40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B41" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C41" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
@@ -2505,7 +2505,7 @@
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
       <c r="T41" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="U41" s="2"/>
       <c r="V41" s="2"/>
@@ -2513,23 +2513,23 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C42" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -2544,19 +2544,19 @@
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
       <c r="V42" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="W42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B43" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C43" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -2569,7 +2569,7 @@
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" s="2"/>
@@ -2583,18 +2583,18 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B44" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C44" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -2616,19 +2616,19 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B45" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C45" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -2639,10 +2639,10 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P45" s="2"/>
       <c r="Q45" s="2"/>
@@ -2651,25 +2651,25 @@
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
       <c r="V45" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="W45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B46" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C46" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
@@ -2690,13 +2690,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B47" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C47" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
@@ -2709,7 +2709,7 @@
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
       <c r="N47" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
@@ -2723,13 +2723,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B48" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C48" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -2737,23 +2737,23 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
       <c r="R48" s="2"/>
       <c r="S48" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
@@ -2850,7 +2850,7 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -2867,31 +2867,41 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="M2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
+      <c r="P2" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
+      <c r="S2" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
+      <c r="U2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="W2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="2" t="n">
         <v>2</v>
       </c>
@@ -2916,25 +2926,23 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
-      <c r="U3" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="U3" s="2"/>
       <c r="V3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>1</v>
@@ -2946,7 +2954,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -2965,19 +2973,17 @@
         <v>1</v>
       </c>
       <c r="V4" s="2"/>
-      <c r="W4" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="W4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2</v>
@@ -3016,13 +3022,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="n">
@@ -3063,13 +3069,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="n">
@@ -3110,13 +3116,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>1</v>
@@ -3131,7 +3137,7 @@
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -3155,13 +3161,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>1</v>
@@ -3200,13 +3206,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>1</v>
@@ -3243,13 +3249,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -3286,13 +3292,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -3335,13 +3341,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2</v>
@@ -3392,13 +3398,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>1</v>
@@ -3437,13 +3443,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>1</v>
@@ -3490,13 +3496,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>4</v>
@@ -3531,13 +3537,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>4</v>
@@ -3572,13 +3578,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="n">
@@ -3621,13 +3627,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>1</v>
@@ -3657,7 +3663,9 @@
         <v>2</v>
       </c>
       <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
+      <c r="P19" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Q19" s="2" t="n">
         <v>1</v>
       </c>
@@ -3674,13 +3682,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="n">
@@ -3719,13 +3727,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>1</v>
@@ -3735,9 +3743,7 @@
       <c r="G21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H21" s="2"/>
       <c r="I21" s="2" t="n">
         <v>1</v>
       </c>
@@ -3756,7 +3762,9 @@
       <c r="R21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="S21" s="2"/>
+      <c r="S21" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
       <c r="V21" s="2" t="n">
@@ -3768,13 +3776,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>1</v>
@@ -3819,13 +3827,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -3868,13 +3876,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>3</v>
@@ -3913,13 +3921,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -3930,7 +3938,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -3951,7 +3959,9 @@
         <v>3</v>
       </c>
       <c r="S25" s="2"/>
-      <c r="T25" s="2"/>
+      <c r="T25" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="U25" s="2" t="n">
         <v>2</v>
       </c>
@@ -3960,13 +3970,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>1</v>
@@ -4003,13 +4013,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B27" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2</v>
@@ -4048,13 +4058,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -4089,17 +4099,19 @@
       <c r="V28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W28" s="2"/>
+      <c r="W28" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>1</v>
@@ -4140,13 +4152,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B30" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>1</v>
@@ -4171,7 +4183,9 @@
       <c r="N30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O30" s="2"/>
+      <c r="O30" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="P30" s="2" t="n">
         <v>2</v>
       </c>
@@ -4191,13 +4205,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="n">
@@ -4232,25 +4246,21 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B32" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C32" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="2"/>
-      <c r="G32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
       <c r="I32" s="2" t="n">
         <v>1</v>
       </c>
@@ -4285,13 +4295,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2" t="n">
@@ -4338,13 +4348,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2" t="n">
@@ -4387,13 +4397,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C35" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -4405,7 +4415,9 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
+      <c r="L35" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="M35" s="2" t="n">
         <v>1</v>
       </c>
@@ -4432,13 +4444,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B36" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>1</v>
@@ -4485,13 +4497,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B37" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C37" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -4524,31 +4536,27 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C38" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="2"/>
-      <c r="G38" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
-      <c r="N38" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2" t="n">
         <v>1</v>
       </c>
@@ -4565,13 +4573,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B39" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C39" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -4580,9 +4588,7 @@
       <c r="H39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I39" s="2"/>
       <c r="J39" s="2" t="n">
         <v>1</v>
       </c>
@@ -4593,9 +4599,7 @@
       <c r="O39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P39" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P39" s="2"/>
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
@@ -4610,13 +4614,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B40" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>2</v>
@@ -4657,13 +4661,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B41" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C41" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>1</v>
@@ -4687,7 +4691,7 @@
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P41" s="2"/>
       <c r="Q41" s="2"/>
@@ -4700,19 +4704,17 @@
       <c r="V41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W41" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="W41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C42" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>1</v>
@@ -4724,7 +4726,9 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
+      <c r="J42" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -4747,13 +4751,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B43" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C43" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2" t="n">
@@ -4794,13 +4798,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B44" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C44" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
@@ -4810,7 +4814,7 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -4843,13 +4847,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B45" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C45" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -4888,13 +4892,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B46" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C46" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
@@ -4923,13 +4927,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B47" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C47" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>1</v>
@@ -4968,13 +4972,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B48" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C48" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>1</v>
@@ -5009,13 +5013,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B49" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C49" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>2</v>
@@ -5052,45 +5056,6 @@
       </c>
       <c r="W49" s="2"/>
     </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" t="s">
-        <v>226</v>
-      </c>
-      <c r="C50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" s="2"/>
-      <c r="P50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" s="2"/>
-      <c r="S50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T50" s="2"/>
-      <c r="U50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V50" s="2"/>
-      <c r="W50" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/fifa_2026_sticker_trade.xlsx
+++ b/fifa_2026_sticker_trade.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -150,9 +150,6 @@
     <t xml:space="preserve">BIH</t>
   </si>
   <si>
-    <t xml:space="preserve">BIH_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">BIH_11</t>
   </si>
   <si>
@@ -210,9 +207,6 @@
     <t xml:space="preserve">HAI</t>
   </si>
   <si>
-    <t xml:space="preserve">HAI_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">HAI_12</t>
   </si>
   <si>
@@ -388,9 +382,6 @@
   </si>
   <si>
     <t xml:space="preserve">BEL_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEL_5</t>
   </si>
   <si>
     <t xml:space="preserve">Egypt</t>
@@ -1295,9 +1286,7 @@
         <v>44</v>
       </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -1307,7 +1296,7 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
@@ -1324,10 +1313,10 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
         <v>47</v>
-      </c>
-      <c r="C8" t="s">
-        <v>48</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -1343,11 +1332,11 @@
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R8" s="2"/>
       <c r="S8" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
@@ -1359,10 +1348,10 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
         <v>51</v>
-      </c>
-      <c r="C9" t="s">
-        <v>52</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -1375,7 +1364,7 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
@@ -1389,18 +1378,18 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
         <v>54</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>56</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -1412,31 +1401,31 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
         <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>61</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -1459,19 +1448,17 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
         <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>64</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2" t="s">
-        <v>65</v>
-      </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1481,7 +1468,7 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
@@ -1494,13 +1481,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -1511,10 +1498,10 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -1529,13 +1516,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -1552,7 +1539,7 @@
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
@@ -1562,18 +1549,18 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -1592,28 +1579,28 @@
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
       <c r="W15" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -1628,19 +1615,19 @@
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
       <c r="V16" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="W16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -1651,7 +1638,7 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -1660,10 +1647,10 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
       <c r="S17" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
@@ -1671,13 +1658,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s">
         <v>88</v>
-      </c>
-      <c r="B18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" t="s">
-        <v>90</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -1686,7 +1673,7 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
@@ -1704,20 +1691,20 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -1726,12 +1713,12 @@
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
@@ -1741,13 +1728,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -1762,13 +1749,13 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
@@ -1776,13 +1763,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -1797,7 +1784,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
@@ -1809,13 +1796,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" t="s">
         <v>104</v>
-      </c>
-      <c r="B22" t="s">
-        <v>105</v>
-      </c>
-      <c r="C22" t="s">
-        <v>106</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -1825,7 +1812,7 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -1842,13 +1829,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -1861,7 +1848,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -1869,7 +1856,7 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
@@ -1877,13 +1864,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -1895,7 +1882,7 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -1910,18 +1897,18 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -1935,37 +1922,35 @@
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="S25" s="2"/>
       <c r="T25" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="U25" s="2"/>
       <c r="V25" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="W25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" t="s">
         <v>121</v>
-      </c>
-      <c r="B26" t="s">
-        <v>122</v>
-      </c>
-      <c r="C26" t="s">
-        <v>123</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G26" s="2"/>
-      <c r="H26" s="2" t="s">
-        <v>125</v>
-      </c>
+      <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -1984,27 +1969,27 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -2013,7 +1998,7 @@
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
       <c r="R27" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
@@ -2023,17 +2008,17 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B28" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C28" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -2049,30 +2034,30 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
       <c r="S28" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
       <c r="W28" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B29" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -2093,13 +2078,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B30" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C30" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -2117,7 +2102,7 @@
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
       <c r="S30" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
@@ -2126,13 +2111,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B31" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C31" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -2151,7 +2136,7 @@
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
       <c r="T31" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
@@ -2159,16 +2144,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B32" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C32" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -2189,21 +2174,21 @@
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
       <c r="W32" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B33" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C33" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -2213,7 +2198,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -2229,18 +2214,18 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B34" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C34" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -2252,7 +2237,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
@@ -2264,13 +2249,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B35" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C35" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -2279,7 +2264,7 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
@@ -2297,13 +2282,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B36" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C36" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -2312,7 +2297,7 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
@@ -2330,13 +2315,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B37" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C37" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -2347,7 +2332,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
@@ -2363,26 +2348,26 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B38" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C38" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -2390,11 +2375,11 @@
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="S38" s="2"/>
       <c r="T38" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="U38" s="2"/>
       <c r="V38" s="2"/>
@@ -2402,17 +2387,17 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B39" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C39" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -2420,17 +2405,17 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
       <c r="Q39" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
@@ -2441,13 +2426,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B40" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C40" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
@@ -2460,10 +2445,10 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
@@ -2471,22 +2456,22 @@
       <c r="S40" s="2"/>
       <c r="T40" s="2"/>
       <c r="U40" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="W40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B41" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C41" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
@@ -2505,7 +2490,7 @@
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
       <c r="T41" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="U41" s="2"/>
       <c r="V41" s="2"/>
@@ -2513,23 +2498,23 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B42" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C42" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -2544,19 +2529,19 @@
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
       <c r="V42" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="W42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B43" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C43" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -2569,7 +2554,7 @@
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" s="2"/>
@@ -2583,18 +2568,18 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B44" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C44" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -2616,19 +2601,19 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>200</v>
+      </c>
+      <c r="B45" t="s">
+        <v>201</v>
+      </c>
+      <c r="C45" t="s">
+        <v>202</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B45" t="s">
+      <c r="E45" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="C45" t="s">
-        <v>205</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -2639,10 +2624,10 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P45" s="2"/>
       <c r="Q45" s="2"/>
@@ -2651,25 +2636,25 @@
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
       <c r="V45" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="W45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B46" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C46" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
@@ -2690,13 +2675,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B47" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C47" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
@@ -2709,7 +2694,7 @@
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
       <c r="N47" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
@@ -2723,13 +2708,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B48" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C48" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -2737,23 +2722,23 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
       <c r="R48" s="2"/>
       <c r="S48" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
@@ -3025,10 +3010,10 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="n">
@@ -3164,10 +3149,10 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
         <v>47</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>1</v>
@@ -3209,10 +3194,10 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
         <v>51</v>
-      </c>
-      <c r="C10" t="s">
-        <v>52</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>1</v>
@@ -3249,13 +3234,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
         <v>54</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>55</v>
-      </c>
-      <c r="C11" t="s">
-        <v>56</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -3292,13 +3277,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
         <v>60</v>
-      </c>
-      <c r="C12" t="s">
-        <v>61</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -3341,13 +3326,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
         <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>64</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2</v>
@@ -3398,13 +3383,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>1</v>
@@ -3443,13 +3428,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>1</v>
@@ -3496,13 +3481,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>4</v>
@@ -3537,13 +3522,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>4</v>
@@ -3578,13 +3563,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="n">
@@ -3627,13 +3612,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" t="s">
         <v>88</v>
-      </c>
-      <c r="B19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" t="s">
-        <v>90</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>1</v>
@@ -3682,13 +3667,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="n">
@@ -3727,13 +3712,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>1</v>
@@ -3776,13 +3761,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>1</v>
@@ -3827,13 +3812,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" t="s">
         <v>104</v>
-      </c>
-      <c r="B23" t="s">
-        <v>105</v>
-      </c>
-      <c r="C23" t="s">
-        <v>106</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -3876,13 +3861,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>3</v>
@@ -3921,13 +3906,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -3970,13 +3955,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B26" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>1</v>
@@ -4013,13 +3998,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" t="s">
         <v>121</v>
-      </c>
-      <c r="B27" t="s">
-        <v>122</v>
-      </c>
-      <c r="C27" t="s">
-        <v>123</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2</v>
@@ -4058,13 +4043,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -4105,13 +4090,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B29" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>1</v>
@@ -4152,13 +4137,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B30" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C30" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>1</v>
@@ -4205,13 +4190,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B31" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="n">
@@ -4246,13 +4231,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B32" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C32" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2" t="n">
@@ -4295,13 +4280,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B33" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C33" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2" t="n">
@@ -4348,13 +4333,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B34" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C34" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2" t="n">
@@ -4397,13 +4382,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B35" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C35" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -4444,13 +4429,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B36" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C36" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>1</v>
@@ -4497,13 +4482,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B37" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C37" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -4536,13 +4521,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B38" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C38" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2" t="n">
@@ -4573,13 +4558,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B39" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C39" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -4614,13 +4599,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B40" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C40" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>2</v>
@@ -4661,13 +4646,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B41" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C41" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>1</v>
@@ -4708,13 +4693,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B42" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C42" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>1</v>
@@ -4751,13 +4736,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B43" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C43" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2" t="n">
@@ -4798,13 +4783,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B44" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C44" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
@@ -4847,13 +4832,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B45" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C45" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -4892,13 +4877,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B46" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C46" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
@@ -4927,13 +4912,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B47" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C47" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>1</v>
@@ -4972,13 +4957,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B48" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C48" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>1</v>
@@ -5013,13 +4998,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B49" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C49" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>2</v>

--- a/fifa_2026_sticker_trade.xlsx
+++ b/fifa_2026_sticker_trade.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -267,9 +267,6 @@
     <t xml:space="preserve">TUR_9</t>
   </si>
   <si>
-    <t xml:space="preserve">TUR_16</t>
-  </si>
-  <si>
     <t xml:space="preserve">TUR_17</t>
   </si>
   <si>
@@ -306,9 +303,6 @@
     <t xml:space="preserve">CIV</t>
   </si>
   <si>
-    <t xml:space="preserve">CIV_13</t>
-  </si>
-  <si>
     <t xml:space="preserve">CIV_17</t>
   </si>
   <si>
@@ -468,9 +462,6 @@
     <t xml:space="preserve">URU_1</t>
   </si>
   <si>
-    <t xml:space="preserve">URU_9</t>
-  </si>
-  <si>
     <t xml:space="preserve">I</t>
   </si>
   <si>
@@ -483,9 +474,6 @@
     <t xml:space="preserve">FRA_3</t>
   </si>
   <si>
-    <t xml:space="preserve">FRA_13</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senegal</t>
   </si>
   <si>
@@ -504,181 +492,175 @@
     <t xml:space="preserve">IRQ_7</t>
   </si>
   <si>
+    <t xml:space="preserve">J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argentina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARG_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARG_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARG_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARG_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algeria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALG_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALG_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALG_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALG_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUT_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUT_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUT_18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUT_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOR_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portugal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POR_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POR_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POR_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Congo DR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COD_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">England</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENG_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croatia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRO_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GHA_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CZE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Norway</t>
   </si>
   <si>
     <t xml:space="preserve">NOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOR_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argentina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARG_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARG_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARG_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARG_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algeria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALG_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALG_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALG_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALG_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUT_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUT_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUT_18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUT_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOR_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portugal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POR_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POR_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POR_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Congo DR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COD_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colombia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">England</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENG_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Croatia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRO_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GHA_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CZE</t>
   </si>
   <si>
     <t xml:space="preserve">Uzbekistan</t>
@@ -1646,11 +1628,9 @@
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
-      <c r="S17" s="2" t="s">
+      <c r="S17" s="2"/>
+      <c r="T17" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
@@ -1658,13 +1638,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s">
         <v>86</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>87</v>
-      </c>
-      <c r="C18" t="s">
-        <v>88</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -1673,7 +1653,7 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
@@ -1691,20 +1671,20 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" t="s">
         <v>90</v>
-      </c>
-      <c r="C19" t="s">
-        <v>91</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -1713,12 +1693,12 @@
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
@@ -1728,13 +1708,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" t="s">
         <v>95</v>
-      </c>
-      <c r="C20" t="s">
-        <v>96</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -1748,14 +1728,12 @@
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="2" t="s">
-        <v>97</v>
-      </c>
+      <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
@@ -1763,13 +1741,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -1784,7 +1762,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
@@ -1796,13 +1774,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" t="s">
         <v>102</v>
-      </c>
-      <c r="B22" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" t="s">
-        <v>104</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -1812,7 +1790,7 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -1829,13 +1807,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -1848,7 +1826,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -1856,7 +1834,7 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
@@ -1864,13 +1842,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -1882,7 +1860,7 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -1897,18 +1875,18 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -1922,32 +1900,32 @@
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="S25" s="2"/>
       <c r="T25" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="U25" s="2"/>
       <c r="V25" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="W25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" t="s">
         <v>119</v>
-      </c>
-      <c r="B26" t="s">
-        <v>120</v>
-      </c>
-      <c r="C26" t="s">
-        <v>121</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -1969,27 +1947,27 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="C27" t="s">
-        <v>124</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -1998,7 +1976,7 @@
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
       <c r="R27" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
@@ -2008,17 +1986,17 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -2034,30 +2012,30 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
       <c r="S28" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
       <c r="W28" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C29" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -2078,13 +2056,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>135</v>
+      </c>
+      <c r="B30" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" t="s">
         <v>137</v>
-      </c>
-      <c r="B30" t="s">
-        <v>138</v>
-      </c>
-      <c r="C30" t="s">
-        <v>139</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -2102,7 +2080,7 @@
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
       <c r="S30" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
@@ -2111,13 +2089,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B31" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C31" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -2136,7 +2114,7 @@
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
       <c r="T31" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
@@ -2144,16 +2122,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B32" t="s">
+        <v>142</v>
+      </c>
+      <c r="C32" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="C32" t="s">
-        <v>145</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -2174,21 +2152,21 @@
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
       <c r="W32" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B33" t="s">
+        <v>146</v>
+      </c>
+      <c r="C33" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="C33" t="s">
-        <v>149</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -2197,9 +2175,7 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-      <c r="L33" s="2" t="s">
-        <v>151</v>
-      </c>
+      <c r="L33" s="2"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -2214,18 +2190,18 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B34" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C34" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -2236,9 +2212,7 @@
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
-      <c r="P34" s="2" t="s">
-        <v>156</v>
-      </c>
+      <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
@@ -2249,13 +2223,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B35" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C35" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -2264,7 +2238,7 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
@@ -2282,13 +2256,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B36" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C36" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -2297,7 +2271,7 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
@@ -2315,57 +2289,65 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B37" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C37" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
+      <c r="H37" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
-      <c r="R37" s="2"/>
+      <c r="R37" s="2" t="s">
+        <v>164</v>
+      </c>
       <c r="S37" s="2"/>
-      <c r="T37" s="2"/>
+      <c r="T37" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="U37" s="2"/>
       <c r="V37" s="2"/>
       <c r="W37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>159</v>
+      </c>
+      <c r="B38" t="s">
         <v>166</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>167</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" s="2"/>
+      <c r="E38" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-      <c r="H38" s="2" t="s">
-        <v>169</v>
-      </c>
+      <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
+      <c r="K38" s="2" t="s">
+        <v>169</v>
+      </c>
       <c r="L38" s="2" t="s">
         <v>170</v>
       </c>
@@ -2373,66 +2355,64 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
-      <c r="Q38" s="2"/>
-      <c r="R38" s="2" t="s">
+      <c r="Q38" s="2" t="s">
         <v>171</v>
       </c>
+      <c r="R38" s="2"/>
       <c r="S38" s="2"/>
-      <c r="T38" s="2" t="s">
-        <v>172</v>
-      </c>
+      <c r="T38" s="2"/>
       <c r="U38" s="2"/>
       <c r="V38" s="2"/>
       <c r="W38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B39" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39" t="s">
         <v>173</v>
       </c>
-      <c r="C39" t="s">
-        <v>174</v>
-      </c>
       <c r="D39" s="2"/>
-      <c r="E39" s="2" t="s">
-        <v>175</v>
-      </c>
+      <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
       <c r="M39" s="2"/>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="N39" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>175</v>
+      </c>
       <c r="P39" s="2"/>
-      <c r="Q39" s="2" t="s">
-        <v>178</v>
-      </c>
+      <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
       <c r="T39" s="2"/>
-      <c r="U39" s="2"/>
-      <c r="V39" s="2"/>
+      <c r="U39" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="V39" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="W39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B40" t="s">
+        <v>178</v>
+      </c>
+      <c r="C40" t="s">
         <v>179</v>
-      </c>
-      <c r="C40" t="s">
-        <v>180</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
@@ -2444,41 +2424,39 @@
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
-      <c r="N40" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>182</v>
-      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
-      <c r="T40" s="2"/>
-      <c r="U40" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="V40" s="2" t="s">
-        <v>184</v>
-      </c>
+      <c r="T40" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="U40" s="2"/>
+      <c r="V40" s="2"/>
       <c r="W40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B41" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C41" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
+      <c r="H41" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>185</v>
+      </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
@@ -2489,38 +2467,36 @@
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
-      <c r="T41" s="2" t="s">
-        <v>187</v>
-      </c>
+      <c r="T41" s="2"/>
       <c r="U41" s="2"/>
-      <c r="V41" s="2"/>
+      <c r="V41" s="2" t="s">
+        <v>186</v>
+      </c>
       <c r="W41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>181</v>
+      </c>
+      <c r="B42" t="s">
+        <v>187</v>
+      </c>
+      <c r="C42" t="s">
         <v>188</v>
-      </c>
-      <c r="B42" t="s">
-        <v>189</v>
-      </c>
-      <c r="C42" t="s">
-        <v>190</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>192</v>
-      </c>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
-      <c r="N42" s="2"/>
+      <c r="N42" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
       <c r="Q42" s="2"/>
@@ -2528,24 +2504,24 @@
       <c r="S42" s="2"/>
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
-      <c r="V42" s="2" t="s">
-        <v>193</v>
-      </c>
+      <c r="V42" s="2"/>
       <c r="W42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B43" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C43" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
+      <c r="F43" s="2" t="s">
+        <v>192</v>
+      </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
@@ -2553,9 +2529,7 @@
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
-      <c r="N43" s="2" t="s">
-        <v>196</v>
-      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" s="2"/>
       <c r="Q43" s="2"/>
@@ -2568,19 +2542,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B44" t="s">
+        <v>194</v>
+      </c>
+      <c r="C44" t="s">
+        <v>195</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C44" t="s">
-        <v>198</v>
-      </c>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2" t="s">
-        <v>199</v>
-      </c>
+      <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
@@ -2588,7 +2564,9 @@
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
+      <c r="N44" s="2" t="s">
+        <v>198</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" s="2"/>
       <c r="Q44" s="2"/>
@@ -2596,73 +2574,67 @@
       <c r="S44" s="2"/>
       <c r="T44" s="2"/>
       <c r="U44" s="2"/>
-      <c r="V44" s="2"/>
+      <c r="V44" s="2" t="s">
+        <v>199</v>
+      </c>
       <c r="W44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>193</v>
+      </c>
+      <c r="B45" t="s">
         <v>200</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>201</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
-      <c r="N45" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="O45" s="2" t="s">
-        <v>206</v>
-      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" s="2"/>
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
       <c r="S45" s="2"/>
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
-      <c r="V45" s="2" t="s">
-        <v>207</v>
-      </c>
+      <c r="V45" s="2"/>
       <c r="W45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B46" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C46" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="2" t="s">
-        <v>210</v>
-      </c>
+      <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
+      <c r="N46" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
       <c r="Q46" s="2"/>
@@ -2675,75 +2647,42 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B47" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C47" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
+      <c r="I47" s="2" t="s">
+        <v>208</v>
+      </c>
       <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
+      <c r="K47" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
       <c r="N47" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
       <c r="Q47" s="2"/>
       <c r="R47" s="2"/>
-      <c r="S47" s="2"/>
+      <c r="S47" s="2" t="s">
+        <v>211</v>
+      </c>
       <c r="T47" s="2"/>
       <c r="U47" s="2"/>
       <c r="V47" s="2"/>
       <c r="W47" s="2"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>200</v>
-      </c>
-      <c r="B48" t="s">
-        <v>214</v>
-      </c>
-      <c r="C48" t="s">
-        <v>215</v>
-      </c>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
-      <c r="N48" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="O48" s="2"/>
-      <c r="P48" s="2"/>
-      <c r="Q48" s="2"/>
-      <c r="R48" s="2"/>
-      <c r="S48" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="T48" s="2"/>
-      <c r="U48" s="2"/>
-      <c r="V48" s="2"/>
-      <c r="W48" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3010,10 +2949,10 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C6" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="n">
@@ -3612,20 +3551,20 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" t="s">
         <v>86</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>87</v>
-      </c>
-      <c r="C19" t="s">
-        <v>88</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="n">
@@ -3642,7 +3581,7 @@
         <v>3</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>2</v>
@@ -3656,9 +3595,7 @@
       </c>
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
-      <c r="T19" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="T19" s="2"/>
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
       <c r="W19" s="2" t="n">
@@ -3667,13 +3604,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" t="s">
         <v>90</v>
-      </c>
-      <c r="C20" t="s">
-        <v>91</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="n">
@@ -3712,13 +3649,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
         <v>95</v>
-      </c>
-      <c r="C21" t="s">
-        <v>96</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>1</v>
@@ -3761,13 +3698,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>1</v>
@@ -3812,13 +3749,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" t="s">
         <v>102</v>
-      </c>
-      <c r="B23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C23" t="s">
-        <v>104</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -3861,13 +3798,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>3</v>
@@ -3906,13 +3843,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -3955,13 +3892,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>1</v>
@@ -3998,13 +3935,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" t="s">
         <v>119</v>
-      </c>
-      <c r="B27" t="s">
-        <v>120</v>
-      </c>
-      <c r="C27" t="s">
-        <v>121</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2</v>
@@ -4043,13 +3980,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B28" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -4090,13 +4027,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>1</v>
@@ -4137,13 +4074,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B30" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C30" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>1</v>
@@ -4190,13 +4127,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" t="s">
         <v>137</v>
-      </c>
-      <c r="B31" t="s">
-        <v>138</v>
-      </c>
-      <c r="C31" t="s">
-        <v>139</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="n">
@@ -4231,24 +4168,20 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B32" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C32" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D32" s="2"/>
-      <c r="E32" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="n">
         <v>1</v>
@@ -4257,9 +4190,7 @@
         <v>1</v>
       </c>
       <c r="M32" s="2"/>
-      <c r="N32" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2" t="n">
         <v>1</v>
@@ -4274,19 +4205,17 @@
       <c r="V32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="W32" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="W32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B33" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C33" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2" t="n">
@@ -4333,13 +4262,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B34" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C34" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2" t="n">
@@ -4382,13 +4311,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B35" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C35" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -4429,13 +4358,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B36" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C36" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>1</v>
@@ -4482,13 +4411,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B37" t="s">
-        <v>163</v>
+        <v>214</v>
       </c>
       <c r="C37" t="s">
-        <v>164</v>
+        <v>215</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -4521,13 +4450,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B38" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C38" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2" t="n">
@@ -4558,13 +4487,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>159</v>
+      </c>
+      <c r="B39" t="s">
         <v>166</v>
       </c>
-      <c r="B39" t="s">
-        <v>173</v>
-      </c>
       <c r="C39" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -4573,7 +4502,9 @@
       <c r="H39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="2"/>
+      <c r="I39" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="J39" s="2" t="n">
         <v>1</v>
       </c>
@@ -4599,13 +4530,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B40" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C40" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>2</v>
@@ -4646,13 +4577,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B41" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C41" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>1</v>
@@ -4693,13 +4624,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B42" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C42" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>1</v>
@@ -4723,9 +4654,7 @@
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
       <c r="Q42" s="2"/>
-      <c r="R42" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="R42" s="2"/>
       <c r="S42" s="2"/>
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
@@ -4736,13 +4665,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>181</v>
+      </c>
+      <c r="B43" t="s">
+        <v>187</v>
+      </c>
+      <c r="C43" t="s">
         <v>188</v>
-      </c>
-      <c r="B43" t="s">
-        <v>194</v>
-      </c>
-      <c r="C43" t="s">
-        <v>195</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2" t="n">
@@ -4783,13 +4712,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B44" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C44" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
@@ -4832,13 +4761,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B45" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C45" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -4877,13 +4806,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B46" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C46" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
@@ -4912,13 +4841,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>193</v>
+      </c>
+      <c r="B47" t="s">
         <v>200</v>
       </c>
-      <c r="B47" t="s">
-        <v>208</v>
-      </c>
       <c r="C47" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>1</v>
@@ -4957,13 +4886,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B48" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C48" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>1</v>
@@ -4998,13 +4927,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B49" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C49" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>2</v>
